--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_nickel/dois_filtering.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_nickel/dois_filtering.xlsx
@@ -620,7 +620,7 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
